--- a/WME_POI_Event_Updater_Template.xlsx
+++ b/WME_POI_Event_Updater_Template.xlsx
@@ -507,7 +507,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=123456.789</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=123456.789</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=234567.890</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=234567.890</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=123456.789</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=123456.789</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=234567.890</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=234567.890</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=123456.789</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=123456.789</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>https://waze.com/editor?env=row&amp;venues=234567.890</t>
+          <t>https://www.waze.com/editor?env=row&amp;lat=0.00000&amp;lon=0.00000&amp;zoomLevel=17&amp;venues=234567.890</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
